--- a/testcases/locations/location-auto-addon.xlsx
+++ b/testcases/locations/location-auto-addon.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2524,12 +2524,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TC-LOC-AAO-016</t>
+          <t xml:space="preserve">TC-LOC-AAO-016</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Item List Is Country-Scoped (Same Across Locations)</t>
+          <t>Wordly Uncheck Persists After Save+Reload</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2547,7 +2547,8 @@
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "Auto Add-On"</t>
+Sample input 1: "Auto Add-On"
+Sample input 2: "Wordly"</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2562,30 +2563,30 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Office 1604 (United States)</t>
+          <t>"Auto Add-On" tab active. "Wordly" is checked (default for 1604)</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>1. Navigate to the "Auto Add-On" tab for location 1604 and count checkbox items - verify 5 items: Encore Music, Wireless Presenter, Express Content Design Session, Wordly, Labor.</t>
+          <t>1. Navigate fresh to location 1604, click the "Auto Add-On" tab, and verify "Wordly" is checked.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>The Auto Add-On panel displays 5 checkbox items: Encore Music, Wireless Presenter, Express Content Design Session, Wordly, and Labor.</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Requires a second location whose add-on configuration differs from the standard test office; cannot be exercised from the standard test office</t>
-        </is>
-      </c>
+          <t>The Wordly checkbox is checked.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
@@ -2600,79 +2601,35 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2. Navigate to a different location in the same country and count items - verify the same 5 items appear (the list does not change per location)</t>
+          <t>2. Uncheck "Wordly" and verify Save enables.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>The Auto Add-On checkbox list does NOT change per location - it is the same set for every location within a country (5 items for United States locations including 1604). A different country could present a different set, but that variation is not reachable from a single United States office</t>
+          <t>The Wordly checkbox becomes unchecked and the Save button becomes enabled.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>TC-LOC-AAO-017</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Wordly Uncheck Persists After Save+Reload</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>auto_addon</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Auto Add-On"
-Sample input 2: "Wordly"</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>"Auto Add-On" tab active. "Wordly" is checked (default for 1604)</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>1. Navigate fresh to location 1604, click the "Auto Add-On" tab, and verify "Wordly" is checked.</t>
+          <t>3. Click "Save", then "Ok" and verify the toast appears and save completes.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>The Wordly checkbox is checked.</t>
+          <t>The save completes and a confirmation toast is displayed.</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
@@ -2690,12 +2647,12 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2. Uncheck "Wordly" and verify Save enables.</t>
+          <t>4. Navigate fresh to the location settings page and click the "Auto Add-On" tab.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>The Wordly checkbox becomes unchecked and the Save button becomes enabled.</t>
+          <t>The Auto Add-On panel loads fresh with the updated saved values.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
@@ -2713,35 +2670,79 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>3. Click "Save", then "Ok" and verify the toast appears and save completes.</t>
+          <t>5. Observe "Wordly" and verify it is unchecked</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>The save completes and a confirmation toast is displayed.</t>
+          <t>Unchecking Wordly and saving persists the unchecked state through a full page reload</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-AAO-017</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Labor Uncheck Persists After Save+Reload</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>auto_addon</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Auto Add-On"
+Sample input 2: "Labor"</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>"Auto Add-On" tab active. "Labor" is checked (checked by default for office 1604)</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>4. Navigate fresh to the location settings page and click the "Auto Add-On" tab.</t>
+          <t>1. Navigate fresh to location 1604, click the "Auto Add-On" tab, and verify "Labor" is checked.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>The Auto Add-On panel loads fresh with the updated saved values.</t>
+          <t>The Labor checkbox is checked.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
@@ -2759,79 +2760,35 @@
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>5. Observe "Wordly" and verify it is unchecked</t>
+          <t>2. Uncheck "Labor" and verify Save enables.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Unchecking Wordly and saving persists the unchecked state through a full page reload</t>
+          <t>The Labor checkbox becomes unchecked and the Save button becomes enabled.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>TC-LOC-AAO-018</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Labor Uncheck Persists After Save+Reload</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>auto_addon</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Auto Add-On"
-Sample input 2: "Labor"</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>"Auto Add-On" tab active. "Labor" is checked (checked by default for office 1604)</t>
-        </is>
-      </c>
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>1. Navigate fresh to location 1604, click the "Auto Add-On" tab, and verify "Labor" is checked.</t>
+          <t>3. Click "Save", then "Ok" and verify the toast appears and save completes.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>The Labor checkbox is checked.</t>
+          <t>The save completes and a confirmation toast is displayed.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
@@ -2849,12 +2806,12 @@
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2. Uncheck "Labor" and verify Save enables.</t>
+          <t>4. Navigate fresh to the location settings page and click the "Auto Add-On" tab.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>The Labor checkbox becomes unchecked and the Save button becomes enabled.</t>
+          <t>The Auto Add-On panel loads fresh with the updated saved values.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -2872,35 +2829,79 @@
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>3. Click "Save", then "Ok" and verify the toast appears and save completes.</t>
+          <t>5. Observe "Labor" and verify it is unchecked</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>The save completes and a confirmation toast is displayed.</t>
+          <t>Unchecking Labor and saving persists the unchecked state through a full page reload</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-AAO-018</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Cancel Does Not Persist Toggle</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>auto_addon</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Auto Add-On"
+Sample input 2: "Express Content Design Session"</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>"Auto Add-On" tab active. "Express Content Design Session" is unchecked (default)</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>4. Navigate fresh to the location settings page and click the "Auto Add-On" tab.</t>
+          <t>1. Navigate fresh to location 1604 and click the "Auto Add-On" tab.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>The Auto Add-On panel loads fresh with the updated saved values.</t>
+          <t>The Auto Add-On panel is displayed with the default checkbox values loaded.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
@@ -2918,79 +2919,35 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>5. Observe "Labor" and verify it is unchecked</t>
+          <t>2. Click "Express Content Design Session" to check it and verify Save enables.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Unchecking Labor and saving persists the unchecked state through a full page reload</t>
+          <t>The Express Content Design Session checkbox becomes checked and the Save button becomes enabled.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>TC-LOC-AAO-019</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Cancel Does Not Persist Toggle</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>auto_addon</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Auto Add-On"
-Sample input 2: "Express Content Design Session"</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>"Auto Add-On" tab active. "Express Content Design Session" is unchecked (default)</t>
-        </is>
-      </c>
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>1. Navigate fresh to location 1604 and click the "Auto Add-On" tab.</t>
+          <t>3. Click "Save" and verify the dialog appears.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>The Auto Add-On panel is displayed with the default checkbox values loaded.</t>
+          <t>The Save Changes dialog is displayed.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
@@ -3008,12 +2965,12 @@
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2. Click "Express Content Design Session" to check it and verify Save enables.</t>
+          <t>4. Click "Cancel" and verify the dialog closes with the pending change preserved.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>The Express Content Design Session checkbox becomes checked and the Save button becomes enabled.</t>
+          <t>The dialog closes and the Express Content Design Session checkbox remains checked.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -3031,12 +2988,12 @@
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>3. Click "Save" and verify the dialog appears.</t>
+          <t>5. Navigate fresh to the location settings page and click the "Auto Add-On" tab.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>The Save Changes dialog is displayed.</t>
+          <t>The Auto Add-On panel loads fresh with the original saved values.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
@@ -3054,35 +3011,83 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>4. Click "Cancel" and verify the dialog closes with the pending change preserved.</t>
+          <t>6. Observe "Express Content Design Session" and verify it is unchecked - cancel did not save</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>The dialog closes and the Express Content Design Session checkbox remains checked.</t>
+          <t>Clicking Cancel in Save dialog does not persist the change. After reload, Express Content Design Session returns to its original unchecked state</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-LOC-AAO-019</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Bulk Invert All Checkboxes Persists After Save+Reload</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>locations</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>auto_addon</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "Auto Add-On"
+Sample input 2: "Encore Music"
+Sample input 3: "Wireless Presenter"
+Sample input 4: "Wordly"
+Sample input 5: "Labor"
+Sample input 6: "Express Content Design Session"</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>"Auto Add-On" tab active. All 5 checkboxes at default state (Encore Music=checked, Wireless Presenter=checked, Express Content Design Session=unchecked, Wordly=checked, Labor=checked)</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>5. Navigate fresh to the location settings page and click the "Auto Add-On" tab.</t>
+          <t>1. Navigate fresh to location 1604 and click the "Auto Add-On" tab.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>The Auto Add-On panel loads fresh with the original saved values.</t>
+          <t>The Auto Add-On panel is displayed with the default checkbox values loaded.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -3100,83 +3105,35 @@
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>6. Observe "Express Content Design Session" and verify it is unchecked - cancel did not save</t>
+          <t>2. Uncheck "Encore Music", "Wireless Presenter", "Wordly", and "Labor", then check "Express Content Design Session" and verify Save becomes enabled.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Clicking Cancel in Save dialog does not persist the change. After reload, Express Content Design Session returns to its original unchecked state</t>
+          <t>All 5 checkboxes reflect the new inverted values and the Save button becomes enabled.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>TC-LOC-AAO-020</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Bulk Invert All Checkboxes Persists After Save+Reload</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>locations</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>auto_addon</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "Auto Add-On"
-Sample input 2: "Encore Music"
-Sample input 3: "Wireless Presenter"
-Sample input 4: "Wordly"
-Sample input 5: "Labor"
-Sample input 6: "Express Content Design Session"</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>"Auto Add-On" tab active. All 5 checkboxes at default state (Encore Music=checked, Wireless Presenter=checked, Express Content Design Session=unchecked, Wordly=checked, Labor=checked)</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>1. Navigate fresh to location 1604 and click the "Auto Add-On" tab.</t>
+          <t>3. Click "Save", then "Ok" and verify the toast appears and save completes.</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>The Auto Add-On panel is displayed with the default checkbox values loaded.</t>
+          <t>The save completes and a confirmation toast is displayed.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
@@ -3194,12 +3151,12 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2. Uncheck "Encore Music", "Wireless Presenter", "Wordly", and "Labor", then check "Express Content Design Session" and verify Save becomes enabled.</t>
+          <t>4. Navigate fresh and click the "Auto Add-On" tab.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>All 5 checkboxes reflect the new inverted values and the Save button becomes enabled.</t>
+          <t>The Auto Add-On panel loads fresh with the updated saved values.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -3217,93 +3174,47 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>3. Click "Save", then "Ok" and verify the toast appears and save completes.</t>
+          <t>5. Verify all 5 are inverted: Encore Music unchecked, Wireless Presenter unchecked, Express Content Design Session checked, Wordly unchecked, Labor unchecked</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>The save completes and a confirmation toast is displayed.</t>
+          <t>All 5 checkbox inversions persist after save+reload. Covers 100% field-instance persistence</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>4. Navigate fresh and click the "Auto Add-On" tab.</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>The Auto Add-On panel loads fresh with the updated saved values.</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr"/>
-    </row>
+    <row r="80"/>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>5. Verify all 5 are inverted: Encore Music unchecked, Wireless Presenter unchecked, Express Content Design Session checked, Wordly unchecked, Labor unchecked</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>All 5 checkbox inversions persist after save+reload. Covers 100% field-instance persistence</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr"/>
-    </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>Location — Auto Add-On</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr"/>
-      <c r="D83" s="2" t="inlineStr"/>
-      <c r="E83" s="2" t="inlineStr"/>
-      <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>Automated: 19 / Pending: 1</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="inlineStr"/>
+      <c r="E81" s="2" t="inlineStr"/>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated: 19 / Pending: 0</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
         <is>
           <t>Pass:19 Fail:0 Skipped:0 Blocked:0</t>
         </is>
       </c>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr">
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>Last Updated: 2026-07-28</t>
         </is>
